--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -35361,118 +35361,517 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G192" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>D116</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
         <is>
           <t>类鼻疽</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="K192" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N190" t="n">
-        <v>0</v>
-      </c>
-      <c r="O190" t="n">
-        <v>0</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="inlineStr">
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO190" t="inlineStr">
+      <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP190" t="inlineStr">
+      <c r="AP192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR190" t="inlineStr">
+      <c r="AR192" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS190" t="inlineStr"/>
-      <c r="AT190" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU190" t="inlineStr">
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV190" t="inlineStr">
+      <c r="AV192" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW190" t="inlineStr">
+      <c r="AW192" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX190" t="inlineStr">
+      <c r="AX192" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY190" t="inlineStr">
+      <c r="AY192" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ190" t="inlineStr">
+      <c r="AZ192" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA190" t="inlineStr">
+      <c r="BA192" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB190" t="inlineStr">
+      <c r="BB192" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC190" t="inlineStr">
+      <c r="BC192" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -35594,7 +35993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -35604,7 +36003,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -35624,7 +36023,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -35799,13 +35799,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -35760,12 +35760,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35790,12 +35790,12 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N192" t="n">
@@ -35804,74 +35804,468 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
+      <c r="P192" t="n">
+        <v>1</v>
+      </c>
       <c r="R192" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1</v>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="n">
+        <v>1</v>
+      </c>
+      <c r="R194" t="n">
         <v>0.001937969923792046</v>
       </c>
-      <c r="S192" t="inlineStr">
+      <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO192" t="inlineStr">
+      <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP192" t="inlineStr">
+      <c r="AP194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR192" t="inlineStr">
+      <c r="AR194" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS192" t="inlineStr"/>
-      <c r="AT192" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV192" t="inlineStr">
+      <c r="AV194" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW192" t="inlineStr">
+      <c r="AW194" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX192" t="inlineStr">
+      <c r="AX194" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY192" t="inlineStr">
+      <c r="AY194" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ192" t="inlineStr">
+      <c r="AZ194" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA192" t="inlineStr">
+      <c r="BA194" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB192" t="inlineStr">
+      <c r="BB194" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC192" t="inlineStr">
+      <c r="BC194" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -35993,7 +36387,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -36003,7 +36397,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -36023,7 +36417,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -36055,7 +36449,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -36271,6 +36271,405 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36304,7 +36703,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -36387,7 +36786,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -36397,7 +36796,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -36417,7 +36816,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -36670,6 +36670,400 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36786,7 +37180,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -36796,7 +37190,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">
@@ -36816,7 +37210,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21275,7 +21275,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23163,7 +23163,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28723,7 +28723,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -29661,7 +29661,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32044,12 +32044,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -32083,13 +32083,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -32122,42 +32122,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32189,12 +32189,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -32219,7 +32219,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -32233,9 +32233,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -32244,82 +32241,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32346,7 +32329,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -32398,98 +32381,23 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
@@ -32583,17 +32491,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -32627,20 +32535,42 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P176" t="n">
-        <v>2</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -32648,6 +32578,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32655,7 +32643,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
@@ -32665,55 +32653,55 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32740,7 +32728,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -32792,98 +32780,18 @@
       <c r="P177" t="n">
         <v>2</v>
       </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R177" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
-        <v>1</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
@@ -32977,17 +32885,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -33012,7 +32920,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -33021,25 +32929,42 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -33047,6 +32972,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN178" t="b">
+        <v>1</v>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33054,7 +33037,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -33064,55 +33047,55 @@
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33139,7 +33122,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -33191,98 +33174,23 @@
       <c r="P179" t="n">
         <v>0</v>
       </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -33376,17 +33284,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33420,93 +33328,173 @@
         </is>
       </c>
       <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
         <v>1</v>
       </c>
-      <c r="O180" t="n">
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT180" t="n">
         <v>1</v>
       </c>
-      <c r="P180" t="n">
-        <v>1</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP180" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="AT180" t="n">
-        <v>2</v>
-      </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33533,7 +33521,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -33585,98 +33573,18 @@
       <c r="P181" t="n">
         <v>1</v>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R181" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -33770,17 +33678,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33805,7 +33713,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -33814,25 +33722,42 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -33840,6 +33765,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33847,7 +33830,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -33857,55 +33840,55 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
         </is>
       </c>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33932,7 +33915,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -33984,98 +33967,23 @@
       <c r="P183" t="n">
         <v>0</v>
       </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -34169,17 +34077,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -34213,93 +34121,173 @@
         </is>
       </c>
       <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
         <v>1</v>
       </c>
-      <c r="O184" t="n">
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT184" t="n">
         <v>1</v>
       </c>
-      <c r="P184" t="n">
-        <v>1</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP184" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="AT184" t="n">
-        <v>2</v>
-      </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34326,7 +34314,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -34378,98 +34366,18 @@
       <c r="P185" t="n">
         <v>1</v>
       </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R185" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -34563,17 +34471,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34598,7 +34506,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -34607,25 +34515,42 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -34633,6 +34558,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34640,7 +34623,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -34650,55 +34633,55 @@
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -34725,7 +34708,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -34777,98 +34760,23 @@
       <c r="P187" t="n">
         <v>0</v>
       </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U187" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN187" t="b">
-        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
@@ -34962,17 +34870,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -35014,12 +34922,34 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -35027,6 +34957,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35034,7 +35022,7 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
@@ -35044,55 +35032,55 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35119,7 +35107,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -35171,98 +35159,18 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -35356,17 +35264,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35391,7 +35299,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -35408,17 +35316,34 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -35426,6 +35351,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35433,7 +35416,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -35443,55 +35426,55 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35518,7 +35501,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -35570,98 +35553,23 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -35755,17 +35663,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35799,93 +35707,173 @@
         </is>
       </c>
       <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
         <v>1</v>
       </c>
-      <c r="O192" t="n">
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT192" t="n">
         <v>1</v>
       </c>
-      <c r="P192" t="n">
-        <v>1</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="AT192" t="n">
-        <v>2</v>
-      </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35912,7 +35900,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -35964,98 +35952,18 @@
       <c r="P193" t="n">
         <v>1</v>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R193" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -36149,17 +36057,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -36184,12 +36092,12 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N194" t="n">
@@ -36198,76 +36106,168 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
-      <c r="R194" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P194" t="n">
+        <v>1</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36299,12 +36299,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -36329,7 +36329,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -36338,98 +36338,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
-      </c>
-      <c r="P195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36456,7 +36439,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -36508,98 +36491,23 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Japan NIID melioidosis notifications; not glanders.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -36693,17 +36601,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36745,12 +36653,34 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -36758,6 +36688,64 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36765,7 +36753,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
@@ -36775,55 +36763,55 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36850,7 +36838,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -36902,98 +36890,18 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MELIOIDOSIS</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -37059,6 +36967,1036 @@
         </is>
       </c>
       <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -37097,7 +38035,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -37180,7 +38118,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -37190,7 +38128,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -37210,7 +38148,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -37242,7 +38180,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -38002,6 +38002,944 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA204" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" t="n">
+        <v>2</v>
+      </c>
+      <c r="P206" t="n">
+        <v>2</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>2</v>
+      </c>
+      <c r="O207" t="n">
+        <v>2</v>
+      </c>
+      <c r="P207" t="n">
+        <v>2</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38035,7 +38973,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -38118,7 +39056,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -38128,7 +39066,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -38148,7 +39086,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -38180,7 +39118,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -38823,118 +38823,517 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>D116</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
         <is>
           <t>类鼻疽</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="inlineStr">
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO208" t="inlineStr">
+      <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP208" t="inlineStr">
+      <c r="AP210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR208" t="inlineStr">
+      <c r="AR210" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS208" t="inlineStr"/>
-      <c r="AT208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU208" t="inlineStr">
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU210" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV208" t="inlineStr">
+      <c r="AV210" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW208" t="inlineStr">
+      <c r="AW210" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX208" t="inlineStr">
+      <c r="AX210" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY208" t="inlineStr">
+      <c r="AY210" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ208" t="inlineStr">
+      <c r="AZ210" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA208" t="inlineStr">
+      <c r="BA210" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB208" t="inlineStr">
+      <c r="BB210" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC208" t="inlineStr">
+      <c r="BC210" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -39056,7 +39455,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -39066,7 +39465,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -39086,7 +39485,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1214,6 +1229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2155,6 +2175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3099,6 +3124,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4043,6 +4073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4987,6 +5022,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5132,6 +5172,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5679,6 +5724,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6221,6 +6271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6369,6 +6424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7313,6 +7373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8257,6 +8322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9201,6 +9271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9346,6 +9421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9893,6 +9973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10435,6 +10520,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10583,6 +10673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11527,6 +11622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12471,6 +12571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13415,6 +13520,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14356,6 +14466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14501,6 +14616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14646,6 +14766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14794,6 +14919,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15738,6 +15868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16682,6 +16817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17626,6 +17766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18567,6 +18712,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18712,6 +18862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18857,6 +19012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19005,6 +19165,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19949,6 +20114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20893,6 +21063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21837,6 +22012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22781,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23722,6 +23907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23867,6 +24057,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24157,6 +24357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25095,6 +25300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26033,6 +26243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26971,6 +27186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27909,6 +28129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28054,6 +28279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28199,6 +28429,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28344,6 +28579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29282,6 +29522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30220,6 +30465,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31158,6 +31408,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32096,6 +32351,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32241,6 +32501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36351,6 +36616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39222,118 +39492,517 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
+      </c>
+      <c r="O210" t="n">
+        <v>1</v>
+      </c>
+      <c r="P210" t="n">
+        <v>1</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" t="n">
+        <v>1</v>
+      </c>
+      <c r="P211" t="n">
+        <v>1</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MELIOIDOSIS; SER_SG_HIST_MELIOIDOSIS</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>D116</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>Melioidosis</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
         <is>
           <t>类鼻疽</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="K212" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N210" t="n">
-        <v>0</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="inlineStr">
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO210" t="inlineStr">
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP210" t="inlineStr">
+      <c r="AP212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR210" t="inlineStr">
+      <c r="AR212" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS210" t="inlineStr"/>
-      <c r="AT210" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU210" t="inlineStr">
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV210" t="inlineStr">
+      <c r="AV212" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW210" t="inlineStr">
+      <c r="AW212" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX210" t="inlineStr">
+      <c r="AX212" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY210" t="inlineStr">
+      <c r="AY212" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ210" t="inlineStr">
+      <c r="AZ212" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA210" t="inlineStr">
+      <c r="BA212" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB210" t="inlineStr">
+      <c r="BB212" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC210" t="inlineStr">
+      <c r="BC212" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -39455,7 +40124,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -39465,7 +40134,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -39485,7 +40154,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -39517,7 +40186,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d116/2026-2029.xlsx
+++ b/diseases/d116/2026-2029.xlsx
@@ -40008,6 +40008,405 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>melioidosis</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Japan NIID melioidosis notifications; not glanders.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_JP_MELIOIDOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40041,7 +40440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -40124,7 +40523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -40134,7 +40533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -40154,7 +40553,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
